--- a/MSME/Test upload format/NewCGMSME.xlsx
+++ b/MSME/Test upload format/NewCGMSME.xlsx
@@ -459,7 +459,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,12 +474,6 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -966,134 +960,134 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1111,8 +1105,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1579,7 +1572,7 @@
       <c r="H2" s="1">
         <v>1</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>32</v>
       </c>
       <c r="J2" s="6" t="s">
@@ -1618,7 +1611,7 @@
       <c r="U2" s="6">
         <v>300000000</v>
       </c>
-      <c r="V2" s="7" t="s">
+      <c r="V2" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W2" s="1">
@@ -1627,16 +1620,16 @@
       <c r="X2" s="6">
         <v>50000000</v>
       </c>
-      <c r="Y2" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="8">
+      <c r="Y2" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="7">
         <v>1</v>
       </c>
       <c r="AA2" s="1">
         <v>24</v>
       </c>
-      <c r="AB2" s="7" t="s">
+      <c r="AB2" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1665,7 +1658,7 @@
       <c r="H3" s="1">
         <v>1</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>44</v>
       </c>
       <c r="J3" s="6" t="s">
@@ -1704,7 +1697,7 @@
       <c r="U3" s="6">
         <v>1000000000</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="V3" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W3" s="1">
@@ -1713,16 +1706,16 @@
       <c r="X3" s="6">
         <v>450000000</v>
       </c>
-      <c r="Y3" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="8">
+      <c r="Y3" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="7">
         <v>1</v>
       </c>
       <c r="AA3" s="1">
         <v>24</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AB3" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1751,7 +1744,7 @@
       <c r="H4" s="1">
         <v>1</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>50</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -1790,7 +1783,7 @@
       <c r="U4" s="6">
         <v>500000000</v>
       </c>
-      <c r="V4" s="7" t="s">
+      <c r="V4" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W4" s="1">
@@ -1799,16 +1792,16 @@
       <c r="X4" s="6">
         <v>150000000</v>
       </c>
-      <c r="Y4" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="8">
+      <c r="Y4" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="7">
         <v>1</v>
       </c>
       <c r="AA4" s="1">
         <v>24</v>
       </c>
-      <c r="AB4" s="7" t="s">
+      <c r="AB4" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1837,7 +1830,7 @@
       <c r="H5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="6" t="s">
         <v>55</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -1876,7 +1869,7 @@
       <c r="U5" s="6">
         <v>500000000</v>
       </c>
-      <c r="V5" s="7" t="s">
+      <c r="V5" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W5" s="1">
@@ -1885,16 +1878,16 @@
       <c r="X5" s="6">
         <v>450000000</v>
       </c>
-      <c r="Y5" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="8">
+      <c r="Y5" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="7">
         <v>1</v>
       </c>
       <c r="AA5" s="1">
         <v>24</v>
       </c>
-      <c r="AB5" s="7" t="s">
+      <c r="AB5" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1923,7 +1916,7 @@
       <c r="H6" s="1">
         <v>1</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="6" t="s">
         <v>59</v>
       </c>
       <c r="J6" s="6" t="s">
@@ -1962,7 +1955,7 @@
       <c r="U6" s="6">
         <v>600000000</v>
       </c>
-      <c r="V6" s="7" t="s">
+      <c r="V6" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W6" s="1">
@@ -1971,16 +1964,16 @@
       <c r="X6" s="6">
         <v>0</v>
       </c>
-      <c r="Y6" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="8">
+      <c r="Y6" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="7">
         <v>1</v>
       </c>
       <c r="AA6" s="1">
         <v>24</v>
       </c>
-      <c r="AB6" s="7" t="s">
+      <c r="AB6" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2009,7 +2002,7 @@
       <c r="H7" s="1">
         <v>1</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="6" t="s">
         <v>63</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -2048,7 +2041,7 @@
       <c r="U7" s="6">
         <v>500000000</v>
       </c>
-      <c r="V7" s="7" t="s">
+      <c r="V7" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W7" s="1">
@@ -2057,16 +2050,16 @@
       <c r="X7" s="6">
         <v>450000000</v>
       </c>
-      <c r="Y7" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="8">
+      <c r="Y7" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="7">
         <v>1</v>
       </c>
       <c r="AA7" s="1">
         <v>24</v>
       </c>
-      <c r="AB7" s="7" t="s">
+      <c r="AB7" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2095,7 +2088,7 @@
       <c r="H8" s="1">
         <v>1</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="6" t="s">
         <v>67</v>
       </c>
       <c r="J8" s="6" t="s">
@@ -2134,7 +2127,7 @@
       <c r="U8" s="6">
         <v>200000000</v>
       </c>
-      <c r="V8" s="7" t="s">
+      <c r="V8" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W8" s="1">
@@ -2143,16 +2136,16 @@
       <c r="X8" s="6">
         <v>50000000</v>
       </c>
-      <c r="Y8" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="8">
+      <c r="Y8" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="7">
         <v>1</v>
       </c>
       <c r="AA8" s="1">
         <v>24</v>
       </c>
-      <c r="AB8" s="7" t="s">
+      <c r="AB8" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2181,7 +2174,7 @@
       <c r="H9" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="6" t="s">
         <v>72</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -2220,7 +2213,7 @@
       <c r="U9" s="6">
         <v>100000000</v>
       </c>
-      <c r="V9" s="7" t="s">
+      <c r="V9" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W9" s="1">
@@ -2229,16 +2222,16 @@
       <c r="X9" s="6">
         <v>50000000</v>
       </c>
-      <c r="Y9" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="8">
+      <c r="Y9" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="7">
         <v>1</v>
       </c>
       <c r="AA9" s="1">
         <v>24</v>
       </c>
-      <c r="AB9" s="7" t="s">
+      <c r="AB9" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2267,7 +2260,7 @@
       <c r="H10" s="1">
         <v>1</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="6" t="s">
         <v>76</v>
       </c>
       <c r="J10" s="6" t="s">
@@ -2306,7 +2299,7 @@
       <c r="U10" s="6">
         <v>150000000</v>
       </c>
-      <c r="V10" s="7" t="s">
+      <c r="V10" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W10" s="1">
@@ -2315,16 +2308,16 @@
       <c r="X10" s="6">
         <v>50000000</v>
       </c>
-      <c r="Y10" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="8">
+      <c r="Y10" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="7">
         <v>1</v>
       </c>
       <c r="AA10" s="1">
         <v>24</v>
       </c>
-      <c r="AB10" s="7" t="s">
+      <c r="AB10" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2353,7 +2346,7 @@
       <c r="H11" s="1">
         <v>1</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="6" t="s">
         <v>80</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -2392,7 +2385,7 @@
       <c r="U11" s="6">
         <v>100000000</v>
       </c>
-      <c r="V11" s="7" t="s">
+      <c r="V11" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W11" s="1">
@@ -2401,16 +2394,16 @@
       <c r="X11" s="6">
         <v>50000000</v>
       </c>
-      <c r="Y11" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="8">
+      <c r="Y11" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="7">
         <v>1</v>
       </c>
       <c r="AA11" s="1">
         <v>24</v>
       </c>
-      <c r="AB11" s="7" t="s">
+      <c r="AB11" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2439,7 +2432,7 @@
       <c r="H12" s="1">
         <v>1</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="6" t="s">
         <v>84</v>
       </c>
       <c r="J12" s="6" t="s">
@@ -2478,7 +2471,7 @@
       <c r="U12" s="6">
         <v>180000000</v>
       </c>
-      <c r="V12" s="7" t="s">
+      <c r="V12" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W12" s="1">
@@ -2487,16 +2480,16 @@
       <c r="X12" s="6">
         <v>50000000</v>
       </c>
-      <c r="Y12" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="8">
+      <c r="Y12" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="7">
         <v>1</v>
       </c>
       <c r="AA12" s="1">
         <v>24</v>
       </c>
-      <c r="AB12" s="7" t="s">
+      <c r="AB12" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2525,7 +2518,7 @@
       <c r="H13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="6" t="s">
         <v>88</v>
       </c>
       <c r="J13" s="6" t="s">
@@ -2564,7 +2557,7 @@
       <c r="U13" s="6">
         <v>20000000</v>
       </c>
-      <c r="V13" s="7" t="s">
+      <c r="V13" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W13" s="1">
@@ -2573,16 +2566,16 @@
       <c r="X13" s="6">
         <v>0</v>
       </c>
-      <c r="Y13" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="8">
+      <c r="Y13" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="7">
         <v>1</v>
       </c>
       <c r="AA13" s="1">
         <v>24</v>
       </c>
-      <c r="AB13" s="7" t="s">
+      <c r="AB13" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2611,7 +2604,7 @@
       <c r="H14" s="1">
         <v>1</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -2650,7 +2643,7 @@
       <c r="U14" s="6">
         <v>300000000</v>
       </c>
-      <c r="V14" s="7" t="s">
+      <c r="V14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W14" s="1">
@@ -2659,16 +2652,16 @@
       <c r="X14" s="6">
         <v>50000000</v>
       </c>
-      <c r="Y14" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="8">
+      <c r="Y14" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="7">
         <v>1</v>
       </c>
       <c r="AA14" s="1">
         <v>24</v>
       </c>
-      <c r="AB14" s="7" t="s">
+      <c r="AB14" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2697,7 +2690,7 @@
       <c r="H15" s="1">
         <v>1</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="6" t="s">
         <v>96</v>
       </c>
       <c r="J15" s="6" t="s">
@@ -2736,7 +2729,7 @@
       <c r="U15" s="6">
         <v>1000000000</v>
       </c>
-      <c r="V15" s="7" t="s">
+      <c r="V15" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W15" s="1">
@@ -2745,16 +2738,16 @@
       <c r="X15" s="6">
         <v>450000000</v>
       </c>
-      <c r="Y15" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="8">
+      <c r="Y15" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="7">
         <v>1</v>
       </c>
       <c r="AA15" s="1">
         <v>24</v>
       </c>
-      <c r="AB15" s="7" t="s">
+      <c r="AB15" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2783,7 +2776,7 @@
       <c r="H16" s="1">
         <v>1</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J16" s="6" t="s">
@@ -2822,7 +2815,7 @@
       <c r="U16" s="6">
         <v>500000000</v>
       </c>
-      <c r="V16" s="7" t="s">
+      <c r="V16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W16" s="1">
@@ -2831,16 +2824,16 @@
       <c r="X16" s="6">
         <v>150000000</v>
       </c>
-      <c r="Y16" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="8">
+      <c r="Y16" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="7">
         <v>1</v>
       </c>
       <c r="AA16" s="1">
         <v>24</v>
       </c>
-      <c r="AB16" s="7" t="s">
+      <c r="AB16" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2869,7 +2862,7 @@
       <c r="H17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="6" t="s">
         <v>104</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -2908,7 +2901,7 @@
       <c r="U17" s="6">
         <v>500000000</v>
       </c>
-      <c r="V17" s="7" t="s">
+      <c r="V17" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W17" s="1">
@@ -2917,16 +2910,16 @@
       <c r="X17" s="6">
         <v>450000000</v>
       </c>
-      <c r="Y17" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="8">
+      <c r="Y17" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="7">
         <v>1</v>
       </c>
       <c r="AA17" s="1">
         <v>24</v>
       </c>
-      <c r="AB17" s="7" t="s">
+      <c r="AB17" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2955,7 +2948,7 @@
       <c r="H18" s="1">
         <v>1</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="6" t="s">
         <v>108</v>
       </c>
       <c r="J18" s="6" t="s">
@@ -2994,7 +2987,7 @@
       <c r="U18" s="6">
         <v>600000000</v>
       </c>
-      <c r="V18" s="7" t="s">
+      <c r="V18" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W18" s="1">
@@ -3003,16 +2996,16 @@
       <c r="X18" s="6">
         <v>0</v>
       </c>
-      <c r="Y18" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="8">
+      <c r="Y18" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="7">
         <v>1</v>
       </c>
       <c r="AA18" s="1">
         <v>24</v>
       </c>
-      <c r="AB18" s="7" t="s">
+      <c r="AB18" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3041,7 +3034,7 @@
       <c r="H19" s="1">
         <v>1</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="6" t="s">
         <v>112</v>
       </c>
       <c r="J19" s="6" t="s">
@@ -3080,7 +3073,7 @@
       <c r="U19" s="6">
         <v>500000000</v>
       </c>
-      <c r="V19" s="7" t="s">
+      <c r="V19" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W19" s="1">
@@ -3089,16 +3082,16 @@
       <c r="X19" s="6">
         <v>450000000</v>
       </c>
-      <c r="Y19" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="8">
+      <c r="Y19" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="7">
         <v>1</v>
       </c>
       <c r="AA19" s="1">
         <v>24</v>
       </c>
-      <c r="AB19" s="7" t="s">
+      <c r="AB19" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3127,7 +3120,7 @@
       <c r="H20" s="1">
         <v>1</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="6" t="s">
         <v>116</v>
       </c>
       <c r="J20" s="6" t="s">
@@ -3166,7 +3159,7 @@
       <c r="U20" s="6">
         <v>200000000</v>
       </c>
-      <c r="V20" s="7" t="s">
+      <c r="V20" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W20" s="1">
@@ -3175,16 +3168,16 @@
       <c r="X20" s="6">
         <v>50000000</v>
       </c>
-      <c r="Y20" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="8">
+      <c r="Y20" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="7">
         <v>1</v>
       </c>
       <c r="AA20" s="1">
         <v>24</v>
       </c>
-      <c r="AB20" s="7" t="s">
+      <c r="AB20" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3213,7 +3206,7 @@
       <c r="H21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="6" t="s">
         <v>120</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -3252,7 +3245,7 @@
       <c r="U21" s="6">
         <v>100000000</v>
       </c>
-      <c r="V21" s="7" t="s">
+      <c r="V21" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W21" s="1">
@@ -3261,16 +3254,16 @@
       <c r="X21" s="6">
         <v>50000000</v>
       </c>
-      <c r="Y21" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="8">
+      <c r="Y21" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="7">
         <v>1</v>
       </c>
       <c r="AA21" s="1">
         <v>24</v>
       </c>
-      <c r="AB21" s="7" t="s">
+      <c r="AB21" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3299,7 +3292,7 @@
       <c r="H22" s="1">
         <v>2</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="6" t="s">
         <v>124</v>
       </c>
       <c r="J22" s="6" t="s">
@@ -3338,7 +3331,7 @@
       <c r="U22" s="6">
         <v>150000000</v>
       </c>
-      <c r="V22" s="7" t="s">
+      <c r="V22" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W22" s="1">
@@ -3347,16 +3340,16 @@
       <c r="X22" s="6">
         <v>50000000</v>
       </c>
-      <c r="Y22" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="8">
+      <c r="Y22" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="7">
         <v>1</v>
       </c>
       <c r="AA22" s="1">
         <v>24</v>
       </c>
-      <c r="AB22" s="7" t="s">
+      <c r="AB22" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3385,7 +3378,7 @@
       <c r="H23" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="6" t="s">
         <v>128</v>
       </c>
       <c r="J23" s="6" t="s">
@@ -3424,7 +3417,7 @@
       <c r="U23" s="6">
         <v>100000000</v>
       </c>
-      <c r="V23" s="7" t="s">
+      <c r="V23" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W23" s="1">
@@ -3433,16 +3426,16 @@
       <c r="X23" s="6">
         <v>50000000</v>
       </c>
-      <c r="Y23" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="8">
+      <c r="Y23" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="7">
         <v>1</v>
       </c>
       <c r="AA23" s="1">
         <v>24</v>
       </c>
-      <c r="AB23" s="7" t="s">
+      <c r="AB23" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3471,7 +3464,7 @@
       <c r="H24" s="1">
         <v>3</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="6" t="s">
         <v>132</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -3510,7 +3503,7 @@
       <c r="U24" s="6">
         <v>180000000</v>
       </c>
-      <c r="V24" s="7" t="s">
+      <c r="V24" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W24" s="1">
@@ -3519,16 +3512,16 @@
       <c r="X24" s="6">
         <v>50000000</v>
       </c>
-      <c r="Y24" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="8">
+      <c r="Y24" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="7">
         <v>1</v>
       </c>
       <c r="AA24" s="1">
         <v>24</v>
       </c>
-      <c r="AB24" s="7" t="s">
+      <c r="AB24" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3557,7 +3550,7 @@
       <c r="H25" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="I25" s="6" t="s">
         <v>136</v>
       </c>
       <c r="J25" s="6" t="s">
@@ -3596,7 +3589,7 @@
       <c r="U25" s="6">
         <v>20000000</v>
       </c>
-      <c r="V25" s="7" t="s">
+      <c r="V25" s="6" t="s">
         <v>40</v>
       </c>
       <c r="W25" s="1">
@@ -3605,16 +3598,16 @@
       <c r="X25" s="6">
         <v>0</v>
       </c>
-      <c r="Y25" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="8">
+      <c r="Y25" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="7">
         <v>1</v>
       </c>
       <c r="AA25" s="1">
         <v>24</v>
       </c>
-      <c r="AB25" s="7" t="s">
+      <c r="AB25" s="6" t="s">
         <v>41</v>
       </c>
     </row>
